--- a/output/reports/cv_experiment_LogisticRegression_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.401436567306519</v>
+        <v>0.1158936023712158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7652244475735372</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7686850772738789</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7677078847255507</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8423087255950443</v>
+        <v>0.9791277787205159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.315376043319702</v>
+        <v>0.2169575691223145</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7652393505542003</v>
+        <v>0.9788177038381292</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7684317202938941</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7674457672264638</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8422924513192496</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.401436567306519</v>
+        <v>0.1158936023712158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7652244475735372</v>
+        <v>0.9788276918439337</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7686850772738789</v>
+        <v>0.9805194805194806</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7677078847255507</v>
+        <v>0.9804195804195804</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8423087255950443</v>
+        <v>0.9791277787205159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': 'balanced', 'C': 1}</t>
+          <t>{'solver': 'lbfgs', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.315376043319702</v>
+        <v>0.2169575691223145</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7652393505542003</v>
+        <v>0.9788177038381292</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7684317202938941</v>
+        <v>0.987012987012987</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7674457672264638</v>
+        <v>0.9869579945799458</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8422924513192496</v>
+        <v>0.9986424571525538</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'saga', 'penalty': 'elasticnet', 'max_iter': 5000, 'l1_ratio': 0.3, 'class_weight': 'balanced', 'C': 10}</t>
+          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_LogisticRegression_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_LogisticRegression_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1158936023712158</v>
+        <v>0.8832416534423828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9788276918439337</v>
+        <v>0.5721182060114788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.6694915254237288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9804195804195804</v>
+        <v>0.6343031364535694</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9791277787205159</v>
+        <v>0.857943119793163</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'C': 10, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l1', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2169575691223145</v>
+        <v>1.199743986129761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9788177038381292</v>
+        <v>0.5785715117558475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6694915254237288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.5965333501821781</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9986424571525538</v>
+        <v>0.8566055012927319</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 0.1, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1158936023712158</v>
+        <v>0.8832416534423828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9788276918439337</v>
+        <v>0.5721182060114788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.6694915254237288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9804195804195804</v>
+        <v>0.6343031364535694</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9791277787205159</v>
+        <v>0.857943119793163</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'solver': 'lbfgs', 'penalty': 'l2', 'max_iter': 5000, 'class_weight': None, 'C': 0.01}</t>
+          <t>{'C': 10, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l1', 'solver': 'saga'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2169575691223145</v>
+        <v>1.199743986129761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9788177038381292</v>
+        <v>0.5785715117558475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.987012987012987</v>
+        <v>0.6694915254237288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9869579945799458</v>
+        <v>0.5965333501821781</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9986424571525538</v>
+        <v>0.8566055012927319</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'solver': 'liblinear', 'penalty': 'l1', 'max_iter': 5000, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 0.1, 'class_weight': None, 'max_iter': 5000, 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
     </row>
